--- a/Excel plots/2026-07-10-NPV_chart_data.xlsx
+++ b/Excel plots/2026-07-10-NPV_chart_data.xlsx
@@ -525,7 +525,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="50"/>
-          <min val="-250"/>
+          <min val="-300"/>
         </scaling>
         <axPos val="l"/>
         <title>
@@ -637,7 +637,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="50"/>
-          <min val="-250"/>
+          <min val="-300"/>
         </scaling>
         <axPos val="l"/>
         <title>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>-250</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="2">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-250, -200, -150, -100, -50, 0, 50</t>
+          <t>-300, -250, -200, -150, -100, -50, 0, 50</t>
         </is>
       </c>
     </row>
